--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.92778126241038</v>
+        <v>10.87576445514169</v>
       </c>
       <c r="D2" t="n">
-        <v>66.82555041395837</v>
+        <v>10.85915194226824</v>
       </c>
       <c r="E2" t="n">
-        <v>7.275058939222392</v>
+        <v>1.182197077623639</v>
       </c>
       <c r="F2" t="n">
-        <v>7.374227185882074</v>
+        <v>1.198311917705837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.87530427378496</v>
+        <v>12.65473694449006</v>
       </c>
       <c r="D3" t="n">
-        <v>77.53818064361379</v>
+        <v>12.59995435458724</v>
       </c>
       <c r="E3" t="n">
-        <v>7.275058939222392</v>
+        <v>1.182197077623639</v>
       </c>
       <c r="F3" t="n">
-        <v>7.374227185882074</v>
+        <v>1.198311917705837</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.22439299905129</v>
+        <v>9.786463862345835</v>
       </c>
       <c r="D4" t="n">
-        <v>59.58677978781095</v>
+        <v>9.682851715519281</v>
       </c>
       <c r="E4" t="n">
-        <v>7.275058939222392</v>
+        <v>1.182197077623639</v>
       </c>
       <c r="F4" t="n">
-        <v>7.374227185882074</v>
+        <v>1.198311917705837</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
